--- a/tests/workbooktests/workbooks/test_ratehelpers.xlsx
+++ b/tests/workbooktests/workbooks/test_ratehelpers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C52C5C-3CA6-4354-BD71-1BB75877B7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82187EA5-48D7-4F9D-B4EA-02793F795343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview Tabs" sheetId="18" r:id="rId1"/>
@@ -748,8 +748,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -765,9 +765,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -805,7 +805,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -911,7 +911,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1062,93 +1062,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340204E2-69E6-4DD5-97B8-ED1481D21F17}">
   <dimension ref="A2:A18"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>187</v>
       </c>
@@ -1161,16 +1161,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65244DF5-80D7-445B-8275-CBDDDF4E3506}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="90.6640625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="77.5546875" style="12" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" customWidth="1"/>
-    <col min="8" max="8" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="90.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="77.5703125" style="12" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>79</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>163</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R7C3OvernightIndex,A</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>82</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIindexFutureRateHelper!R10C3OvernightIndexFutureRateHelper,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>83</v>
       </c>
@@ -1364,13 +1364,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBCB75F-B7E2-417A-B51A-9EA1B0672E67}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.6640625" customWidth="1"/>
-    <col min="2" max="2" width="70.33203125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" customWidth="1"/>
+    <col min="2" max="2" width="70.28515625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>84</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -1419,12 +1419,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>87</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>欣[test_ratehelpers.xlsx]SofrFutureRateHelper!R9C2SofrFutureRateHelper,A</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
@@ -1496,14 +1496,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0B5DD58-D551-4EB6-8795-9A6336CDACCA}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.5546875" customWidth="1"/>
-    <col min="2" max="2" width="103.44140625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.5703125" customWidth="1"/>
+    <col min="2" max="2" width="103.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="106" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D5" s="12"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D6" s="12"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D8" s="12"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D9" s="12"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D10" s="12"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D11" s="12"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>162</v>
       </c>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D15" s="12"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>92</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencySwapR!R16C3ConstNotionalCrossCurrencySwapRateHelper,A</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>7</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>12</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>13</v>
       </c>
@@ -1767,14 +1767,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE987B6-3AFC-4C21-983D-E8670E499AAD}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" customWidth="1"/>
     <col min="2" max="2" width="105" style="12" customWidth="1"/>
     <col min="3" max="3" width="106" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R10C3Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R11C3Euribor,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R12C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>96</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>欣[test_ratehelpers.xlsx]ConstNotionalCrossCurrencyBasis!R17C3ConstNotionalCrossCurrencyBasisSwapRateHelper,A</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>7</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>8</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>11</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>12</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>13</v>
       </c>
@@ -2039,14 +2039,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD913001-8432-46A8-B805-3C8877FF8FEE}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="2" max="2" width="100.88671875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="108.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.28515625" customWidth="1"/>
+    <col min="2" max="2" width="100.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="108.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>167</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R10C3CADLibor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R11C3Euribor,A</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R12C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>101</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>欣[test_ratehelpers.xlsx]MtMCrossCurrencyBasisSwapRateHe!R18C3MtMCrossCurrencyBasisSwapRateHelper,A</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>7</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>8</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>11</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>12</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>13</v>
       </c>
@@ -2322,13 +2322,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96BD365-E285-4A84-8EB5-437F3B693A20}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.5546875" customWidth="1"/>
-    <col min="2" max="2" width="89.109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.5703125" customWidth="1"/>
+    <col min="2" max="2" width="89.140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>168</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R10C2Euribor,A</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>169</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R11C2AUDLibor,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>170</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R12C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>103</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>欣[test_ratehelpers.xlsx]IborIborBasisSwapRateHelper!R14C2IborIborBasisSwapRateHelper,A</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>45756</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>45666</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>45756</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>45756</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>45756</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>104</v>
       </c>
@@ -2510,13 +2510,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4B8905-8681-4349-B601-E6FC9C6EE563}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.88671875" customWidth="1"/>
+    <col min="1" max="1" width="44.85546875" customWidth="1"/>
     <col min="2" max="2" width="94" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>171</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R10C2Sofr,A</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>169</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R11C2AUDLibor,A</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>170</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R12C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>105</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>欣[test_ratehelpers.xlsx]OvernightIborBasisSwapRateHelpe!R13C2OvernightIborBasisSwapRateHelper,A</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>106</v>
       </c>
@@ -2692,13 +2692,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.6640625" customWidth="1"/>
-    <col min="2" max="2" width="82.6640625" customWidth="1"/>
+    <col min="1" max="1" width="42.7109375" customWidth="1"/>
+    <col min="2" max="2" width="82.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R7C2Euribor,A</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -2765,27 +2765,27 @@
         <v>欣[test_ratehelpers.xlsx]MultipleResetsSwapRateHelper!R9C2YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -2798,14 +2798,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA980392-DB4E-4511-92AD-9631BAA7D1FD}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" customWidth="1"/>
-    <col min="2" max="2" width="73.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" customWidth="1"/>
+    <col min="2" max="2" width="73.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2823,10 +2823,10 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R11C2DepositRateHelper,A</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
@@ -2901,58 +2901,58 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="11">
         <f>_xll.qlRateHelperLatestDate(B11)</f>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="11">
         <f>_xll.qlRateHelperEarliestDate(B11)</f>
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="11">
         <f>_xll.qlRateHelperMaturityDate(B11)</f>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(B11)</f>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="11">
         <f>_xll.qlRateHelperPillarDate(B11)</f>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R21C2Euribor,A</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>5</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R22C2DepositRateHelper,A</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>8</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>11</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>13</v>
       </c>
@@ -3033,13 +3033,13 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B29" s="12"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B30" s="12"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R33C2Euribor,A</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>17</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>欣[test_ratehelpers.xlsx]DepositRateHelper!R34C2DepositRateHelper,A</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>7</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>9</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>8</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>11</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>12</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>13</v>
       </c>
@@ -3136,15 +3136,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC39AE1-3C8B-4BAC-BB4F-63180FABE33E}">
   <dimension ref="A1:G67"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" customWidth="1"/>
-    <col min="3" max="3" width="60.109375" customWidth="1"/>
-    <col min="4" max="4" width="52.5546875" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
+    <col min="4" max="4" width="52.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -3162,12 +3162,12 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R15C4FraRateHelper,A</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>8</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>12</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>45845</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>13</v>
       </c>
@@ -3437,17 +3437,17 @@
         <v>45816</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R26C4Euribor,A</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R30C4FraRateHelper,A</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>7</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>8</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>11</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>12</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>13</v>
       </c>
@@ -3645,17 +3645,17 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>18</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>27</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>28</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>115</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R42C4Euribor,A</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>37</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>38</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>39</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>29</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R46C4FraRateHelper,A</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>7</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>9</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>8</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>11</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>45918</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
@@ -3867,17 +3867,17 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="12"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>18</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>30</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R57C4Euribor,A</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>37</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>38</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>39</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>31</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>欣[test_ratehelpers.xlsx]FRARateHelper!R61C4FraRateHelper,A</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>7</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>9</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>8</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>11</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>12</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>13</v>
       </c>
@@ -4084,14 +4084,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AFCFAD-5375-4B86-AD50-9C25C7C81EAE}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.88671875" customWidth="1"/>
-    <col min="2" max="2" width="104.5546875" customWidth="1"/>
+    <col min="1" max="1" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="104.5703125" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -4109,11 +4109,11 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>119</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>120</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>121</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C3FuturesRateHelper,A</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
@@ -4314,13 +4314,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>117</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>122</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R29C3FuturesRateHelper,A</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>7</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>12</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>13</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>54</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>117</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R41C3Euribor,A</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R44C3FuturesRateHelper,A</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>7</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>9</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>8</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>11</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>12</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>54</v>
       </c>
@@ -4651,14 +4651,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F658185D-C335-4A5F-955B-EF5C79D6BAD3}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.109375" customWidth="1"/>
-    <col min="2" max="2" width="65.109375" style="12" customWidth="1"/>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
+    <col min="2" max="2" width="65.140625" style="12" customWidth="1"/>
     <col min="3" max="4" width="71" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -4677,12 +4677,12 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4698,7 +4698,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -4714,7 +4714,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -4733,7 +4733,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -4749,7 +4749,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>128</v>
       </c>
@@ -4765,7 +4765,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>132</v>
       </c>
@@ -4800,7 +4800,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -4814,7 +4814,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>130</v>
       </c>
@@ -4828,7 +4828,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -4872,7 +4872,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -4884,7 +4884,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -4898,7 +4898,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -4912,7 +4912,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R19C4SwapRateHelper,A</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>7</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>8</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>12</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>13</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>51</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>52</v>
       </c>
@@ -5065,13 +5065,13 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R27C4VanillaSwap,A</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>55</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>0</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>47</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>56</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>21</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>57</v>
       </c>
@@ -5158,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>58</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>59</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>60</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R38C4Euribor,A</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>61</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R39C4YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>125</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>136</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R41C4SwapIndex,A</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>133</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R44C4YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>134</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>135</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>120</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>50</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R49C4SwapRateHelper,A</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>7</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>8</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>11</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>12</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>13</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>51</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>52</v>
       </c>
@@ -5480,10 +5480,10 @@
         <v>欣[test_ratehelpers.xlsx]SwapRateHelper!R57C4VanillaSwap,A</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="11"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B63" s="11"/>
     </row>
   </sheetData>
@@ -5498,7 +5498,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5510,33 +5510,33 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A2:I7"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I7" s="1"/>
     </row>
   </sheetData>
@@ -5547,14 +5547,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D8D3E72-38D5-454D-A3CB-8D63AEF54296}">
   <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.44140625" customWidth="1"/>
-    <col min="2" max="2" width="66.88671875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="66.85546875" style="12" customWidth="1"/>
     <col min="3" max="4" width="76" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -5571,10 +5571,10 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>140</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>欣[test_ratehelpers.xlsx]OISRateHelper!R7C4Sofr,A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>153</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>欣[test_ratehelpers.xlsx]OISRateHelper!R8C4YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>143</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>134</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>147</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>156</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>148</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>149</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>150</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -5849,7 +5849,7 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>158</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>65</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>欣[test_ratehelpers.xlsx]OISRateHelper!R29C4OISRateHelper,A</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>7</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>45791</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>12</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>45791</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>13</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>45784</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>64</v>
       </c>
@@ -6032,14 +6032,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C2BEAF-FCDE-48B0-B97E-27F830DD2C98}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.33203125" customWidth="1"/>
-    <col min="2" max="2" width="69.109375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="73.33203125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" customWidth="1"/>
+    <col min="2" max="2" width="69.140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="73.28515625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -6056,10 +6056,10 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R12C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>161</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>69</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>欣[test_ratehelpers.xlsx]FXSwapRateHelper!R14C3FxSwapRateHelper,A</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -6198,72 +6198,72 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="11">
         <f>_xll.qlRateHelperLatestDate(B14)</f>
-        <v>46324</v>
+        <v>45755</v>
       </c>
       <c r="C16" s="11">
         <f>_xll.qlRateHelperLatestDate(C14)</f>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="11">
         <f>_xll.qlRateHelperEarliestDate(B14)</f>
-        <v>46232</v>
+        <v>45665</v>
       </c>
       <c r="C17" s="11">
         <f>_xll.qlRateHelperEarliestDate(C14)</f>
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="11">
         <f>_xll.qlRateHelperMaturityDate(B14)</f>
-        <v>46324</v>
+        <v>45755</v>
       </c>
       <c r="C18" s="11">
         <f>_xll.qlRateHelperMaturityDate(C14)</f>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(B14)</f>
-        <v>46324</v>
+        <v>45755</v>
       </c>
       <c r="C19" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(C14)</f>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="11">
         <f>_xll.qlRateHelperPillarDate(B14)</f>
-        <v>46324</v>
+        <v>45755</v>
       </c>
       <c r="C20" s="11">
         <f>_xll.qlRateHelperPillarDate(C14)</f>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>70</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>71</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>3M</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>72</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>73</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>74</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>75</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>76</v>
       </c>
@@ -6354,26 +6354,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B28" s="12" t="str">
-        <f>_xll.qlFxSwapRateHelperTradingCalendar(B14)</f>
-        <v>Null</v>
       </c>
       <c r="C28" s="12" t="str">
         <f>_xll.qlFxSwapRateHelperTradingCalendar(C14)</f>
         <v>TARGET</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>78</v>
       </c>
       <c r="B29" s="12" t="str">
         <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(B14)</f>
-        <v>JoinHolidays(Null, TARGET)</v>
+        <v>TARGET</v>
       </c>
       <c r="C29" s="12" t="str">
         <f>_xll.qlFxSwapRateHelperAdjustmentCalendar(C14)</f>
